--- a/products-storage/12-otvet-na-pretenziyu/42-reestr-ispolnitelnoy-dokumentacii.xlsx
+++ b/products-storage/12-otvet-na-pretenziyu/42-reestr-ispolnitelnoy-dokumentacii.xlsx
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Статус «передан» или «подписан», а дата или способ передачи не заполнены. Целевое значение — ноль (KPI чек-листа 06): «передал без следа» = «не передал».</t>
+          <t>Статус «передан» или «подписан», а дата или способ передачи не заполнены. Целевое значение — ноль: «передал без следа» = «не передал».</t>
         </is>
       </c>
     </row>
